--- a/artfynd/A 32785-2023 artfynd.xlsx
+++ b/artfynd/A 32785-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32785-2023 artfynd.xlsx
+++ b/artfynd/A 32785-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,6 +1036,243 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118867872</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57306</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>N Evighetsmossen, Heby-Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>616087</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6656727</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Richard Brahmstaedt</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Richard Brahmstaedt</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118867874</v>
+      </c>
+      <c r="B6" t="n">
+        <v>57443</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>N Evighetsmossen, Heby-Råksjön, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>616087</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6656727</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Heby</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Huddunge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>18:39</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>18:45</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Richard Brahmstaedt</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Richard Brahmstaedt</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 32785-2023 artfynd.xlsx
+++ b/artfynd/A 32785-2023 artfynd.xlsx
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118867872</v>
+        <v>118867874</v>
       </c>
       <c r="B5" t="n">
-        <v>57306</v>
+        <v>57443</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,26 +1054,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1154,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118867874</v>
+        <v>118867872</v>
       </c>
       <c r="B6" t="n">
-        <v>57443</v>
+        <v>57306</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1170,31 +1175,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">

--- a/artfynd/A 32785-2023 artfynd.xlsx
+++ b/artfynd/A 32785-2023 artfynd.xlsx
@@ -1038,10 +1038,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118867874</v>
+        <v>118867872</v>
       </c>
       <c r="B5" t="n">
-        <v>57443</v>
+        <v>57306</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1054,31 +1054,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1159,10 +1154,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118867872</v>
+        <v>118867874</v>
       </c>
       <c r="B6" t="n">
-        <v>57306</v>
+        <v>57443</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1175,26 +1170,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">

--- a/artfynd/A 32785-2023 artfynd.xlsx
+++ b/artfynd/A 32785-2023 artfynd.xlsx
@@ -675,62 +675,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95404955</v>
+        <v>95635659</v>
       </c>
       <c r="B2" t="n">
-        <v>57150</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208260</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>N Evighetsmossen, Upl</t>
+          <t>Evighetsmossen, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>616087.3971926067</v>
+        <v>616187</v>
       </c>
       <c r="R2" t="n">
-        <v>6656726.869263995</v>
+        <v>6656606</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -754,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
+          <t>2021-08-22</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-08-07</t>
+          <t>2021-08-22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>09:42</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -778,38 +765,47 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Richard Brahmstaedt</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Richard Brahmstaedt</t>
+          <t>Emil V. Nilsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95635659</v>
+        <v>110943327</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -834,14 +830,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Evighetsmossen, Upl</t>
+          <t>Evighetsmossen, Evighetsmossen, Upl</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>616186.3848412494</v>
+        <v>616155</v>
       </c>
       <c r="R3" t="n">
-        <v>6656605.969092768</v>
+        <v>6656660</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -868,22 +864,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2021-08-22</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2021-08-22</t>
+          <t>2023-07-20</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>09:42</t>
+          <t>09:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,21 +890,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -925,54 +906,52 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110943327</v>
+        <v>118867872</v>
       </c>
       <c r="B4" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Evighetsmossen (Evighetsmossen), Upl</t>
+          <t>N Evighetsmossen, Heby-Råksjön, Upl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>616155.1104304799</v>
+        <v>616087</v>
       </c>
       <c r="R4" t="n">
-        <v>6656660.49275452</v>
+        <v>6656727</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -996,22 +975,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2023-07-20</t>
+          <t>2024-08-02</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1026,27 +1005,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Richard Brahmstaedt</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Emil V. Nilsson</t>
+          <t>Richard Brahmstaedt</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118867872</v>
+        <v>118867874</v>
       </c>
       <c r="B5" t="n">
-        <v>57308</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1054,26 +1028,31 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1154,37 +1133,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>118867874</v>
+        <v>95404955</v>
       </c>
       <c r="B6" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56905</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103021</v>
+        <v>208260</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1192,11 +1166,11 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>N Evighetsmossen, Heby-Råksjön, Upl</t>
@@ -1233,22 +1207,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2021-08-07</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-08-02</t>
+          <t>2021-08-07</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1257,6 +1231,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 32785-2023 artfynd.xlsx
+++ b/artfynd/A 32785-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95635659</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -903,6 +913,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110943327</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1014,6 +1029,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118867872</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1130,6 +1150,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118867874</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1247,8 +1272,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95404955</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>